--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A8F3CD-A840-4A13-B4D5-7D9B4DEB846A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80891007-485A-4350-A0DB-41AB6AC38734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="3930" windowWidth="28740" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="清冊一覽" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
   <si>
     <t>台灣</t>
   </si>
@@ -103,9 +103,6 @@
   <si>
     <t>策展人</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>curators-02</t>
   </si>
   <si>
     <t>策展人/單位中文名</t>
@@ -181,10 +178,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>assets\images\curatorscurators-01.jpg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -678,17 +671,1282 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>assets\images\logos</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
+    <t>文創技研</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>arTecture</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「文創技研」創新有活力，匯聚來自視覺藝術、表演藝術、劇場、舞台道具製作、展場活動規劃等領域的專業優秀人才，策畫執行過多項臺灣大型盛事活動，如台灣燈會、地景藝術節、各式花卉藝術節、博覽會等。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>觸角多元，是亞洲第二個、臺灣第一個獲得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ISO20121</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>活動永續性管理系統</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>組織型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>驗證的公司，將「經濟永續」、「環境永續」和「社會永續」三大目標導入活動，是文創技研的使命及核心。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.artecture-tw.com/h/index?key=r7vnj</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>林晏竹，新媒體藝術家、策展人及研究者，國立臺北藝術大學新媒體藝術碩士、美術學博士。其創作、策展與研究穿越於藝術、資訊技術與宇宙論之間，關注資訊、媒介與系統如何形塑世界及藝術，並探索現實與虛擬、可見與不可見、人與非人間的聯繫。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其策展實踐源自藝術家的經驗，將策展視為一種藝術實踐與創造的方法，使展覽成為一個生成與聯繫不可見的可能場域。曾共同策展關渡光藝術節「量子糾纏」、中山好融異「逾期日常」，以及林茲電子藝術節「震源」、「觀察者模式」、「向星門的迴聲」、「計算演化」等展覽，並策展「訊號世界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[REC]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yen-Ju Lin is a new media artist, curator, and researcher. She holds an MFA in New Media Arts and a PhD in Fine Arts from Taipei National University of the Arts. Her artistic, curatorial, and research practices traverse art, information technology, and cosmological thought, examining how information, media, and systems shape both the world and artistic practice. Her work explores the relations between the real and the virtual, the visible and the invisible, and the human and the inhuman.
+Grounded in her experience as an artist, Lin approaches curating as an artistic practice and a mode of creation, conceiving the exhibition as a generative field in which invisible relations and possibilities can emerge and take form. Her co-curatorial projects include Kuandu Light Art Festival – Quantum Entanglement, Zhongshan Hǎo Róng Yì – Outdated Daily, and Epicentrum, Observer Pattern, Echo Toward the Stargate, and Computational Evolution at Ars Electronica in Linz. She also curated Signal World [REC].</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>共同策展</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「計算演化」，奧地利林茲電子藝術節，林茲，奧地利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「向星門的迴聲」，奧地利林茲電子藝術節，林茲，奧地利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「觀察者模式」，奧地利林茲電子藝術節，林茲，奧地利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「震源」，奧地利林茲電子藝術節，林茲，奧地利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>中山好融異</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>逾期日常」，中山街區，臺北，臺灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2020</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2020</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>關渡光藝術節</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>量子糾纏」，關渡美術館，臺北，臺灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>策展</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「新樂園藝術空間第七屆媒體影像展</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>訊號世界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[REC]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」，新樂園藝術空間，桃園，臺灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>期刊論文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「跨維信使：藝術作品作為一種訊息傳遞媒介」，國立臺灣美術館《臺灣美術學刊》</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>129</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>個展</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2017</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「常常在家</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>林晏竹個展」，福利社，臺北，臺灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>精選聯展</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Can You See Me Now?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The Gem Theater / VTIFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，貝瑟爾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>伯靈頓，緬因州</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>佛蒙特州，美國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「街角的利息」，臺北當代藝術館，臺北，臺灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Non-syntax</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Calm &amp; Punk Gallery / BnA Museum / Workshop Underground</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，東京</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>京都</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>福岡，日本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2021</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「似是而非」，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pa Ta Taipei – PTT Space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，臺北，臺灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2013–2015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Schizophrenia Taiwan 2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」，林茲電子藝術節（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ars Electronica</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>超媒體藝術節</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / Maison des Métallos / Ambika P3 / Instants Video Festival / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>赫勒勞歐洲藝術中心，林茲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>柏林</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>巴黎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>倫敦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>馬賽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>德勒斯登，奧地利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>德國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>法國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>英國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>法國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>德國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2013</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，「第八屆臺北數位藝術節</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>超神經」，松山文創園區，臺北，臺灣</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Co-Curatorial Projects
+2026, Computational Evolution, Ars Electronica Campus, Linz, Austria
+2025, Echo Toward the Stargate, Ars Electronica Campus, Linz, Austria
+2024, Observer Pattern, Ars Electronica Campus, Linz, Austria
+2023, Epicentrum, Ars Electronica Campus, Linz, Austria
+2021, 2021 Zhongshan Hao Rong Yi – Outdated Daily, Zhongshan District, Taipei, Taiwan
+2020, 2020 Kuandu Light Art Festival – Quantum Entanglement, Kuandu Museum of Fine Arts, Taipei, Taiwan
+Curatorial Projects
+2026, The 7th SLY Art Space Media and Moving Image Exhibition — Signal World [REC], SLY Art Space, Taoyuan, Taiwan
+Journal Articles
+2024, “Trans-dimensional Messenger: Artworks as a Media for Information Transmission”, Journal of Taiwanese Art, No. 129, National Taiwan Museum of Fine Arts.
+Solo Exhibitions
+2017, Long Stay – Yen-Ju Lin Solo Exhibition, FreeS Art Space, Taipei, Taiwan
+Selected Group Exhibitions
+2026, Can You See Me Now?, The Gem Theater / VTIFF, Bethel, ME / Burlington, VT, USA
+2024, The Interest from the Street Corner, MOCA Taipei, Taipei, Taiwan
+2021, Non-syntax, Calm &amp; Punk Gallery / BnA Museum / Workshop Underground, Tokyo / Kyoto / Fukuoka, Japan
+2021, Groundless, Pa Ta Taipei – PTT Space, Taipei, Taiwan
+2013–2015, Schizophrenia Taiwan 2.0, Ars Electronica / transmediale / Maison des Métallos / Ambika P3 / Instants Video Festival / HELLERAU – European Centre for the Arts, Linz / Berlin / Paris / London / Marseille / Dresden, Austria / Germany / France / United Kingdom / France / Germany
+2013, 8th Digital Art Festival Taipei – Data-Neurons, Songshan Cultural and Creative Park, Taipei, Taiwan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://linyenju.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>贊助單位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛利浦顯示器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛利浦顯示器承襲品牌深厚的科技底蘊，以創新技術、精準畫質與人性化設計，打造兼具效能與美感的視覺體驗。
+獨特情境光技術可隨畫面內容同步變化，將色彩與光影延伸至螢幕之外，營造更具層次的沉浸氛圍，無論觀影、遊戲或音樂娛樂，都能讓感官全面投入。
+搭配高解析度、流暢更新率、智慧連接與護眼科技，滿足工作與娛樂的多元需求。飛利浦顯示器讓科技自然融入生活，以清晰細節與靈動光影，拓展每一次觀看的精彩視界。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>十銓科技</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c2x3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
       </rPr>
       <t>文創技研</t>
     </r>
@@ -705,109 +1963,291 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>文創技研</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>arTecture</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>「文創技研」創新有活力，匯聚來自視覺藝術、表演藝術、劇場、舞台道具製作、展場活動規劃等領域的專業優秀人才，策畫執行過多項臺灣大型盛事活動，如台灣燈會、地景藝術節、各式花卉藝術節、博覽會等。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>觸角多元，是亞洲第二個、臺灣第一個獲得</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ISO20121</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>活動永續性管理系統</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>組織型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>驗證的公司，將「經濟永續」、「環境永續」和「社會永續」三大目標導入活動，是文創技研的使命及核心。</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.artecture-tw.com/h/index?key=r7vnj</t>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C2x3LOGO.png</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>十銓科技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LOGO-2.png</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\Philips logo.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>十銓科技主要生產自有品牌記憶體模組、各款記憶卡、隨身碟、固態式硬碟、週邊產品系列、行動週邊產品及工規記憶儲存產品，於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2016 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年推出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> T-FORCE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>電競產品系列，並於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2020 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年推出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> T-CREATE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>創作者產品系列。
+十銓科技產品曾獲頒「台北國際電腦展創新設計獎」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Best Choice Award</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、經濟部所頒發的台灣優良設計產品、金點設計獎以及台灣精品獎、享譽國際的日本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> GOOD DESIGN AWARD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>及德國</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> iF Design Award 21 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Red Dot </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>設計大獎等殊榮，並受到全球</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>媒體一致的肯定。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEAMGROUP specializes in the development and production of its own-brand memory modules, memory cards, USB flash drives, solid-state drives (SSDs), peripheral products, mobile accessories, and industrial memory and storage solutions. In 2016, the company launched T-FORCE, its gaming product line, followed by T-CREATE, a product line designed for creators, in 2020.
+TEAMGROUP products have received numerous design awards and international recognition, including the COMPUTEX d&amp;i awards, Best Choice Award, Taiwan Good Design Product Award, Golden Pin Design Award, Taiwan Excellence Awards, Japan’s GOOD DESIGN AWARD, Germany’s iF Design Award 2021 and Red Dot Design Award. Its products have also earned widespread recognition from technology media around the world.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Philips Monitors builds on the brand’s longstanding technological expertise to deliver visual experiences that combine performance and aesthetics through innovative technology, precise image quality, and user-centered design.
+Its exclusive Ambilight technology synchronizes with on-screen content, extending colors and light beyond the display to create a richer, more immersive atmosphere. Whether watching movies, gaming, or enjoying music and entertainment, it brings every experience to life with greater sensory depth.
+With high-resolution displays, smooth refresh rates, smart connectivity, and eye-care technologies, Philips Monitors meets a wide range of needs for both work and entertainment. By seamlessly integrating technology into everyday life, Philips Monitors expands every viewing experience through crisp detail and dynamic light.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>arTecture brings together a dynamic team of professionals from diverse fields, including visual arts, performing arts, theater, stage and prop production, exhibition design, and event planning. The company has planned and delivered numerous major events across Taiwan, including the Taiwan Lantern Festival, land art festivals, floral art festivals, expos, and other large-scale cultural events.
+With expertise spanning a wide range of disciplines, arTecture became the second company in Asia and the first in Taiwan to achieve ISO 20121 certification for its organizational event sustainability management system. Integrating the three pillars of economic, environmental, and social sustainability into event planning and execution lies at the heart of the company’s mission and core values.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Philips</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEAMGROUP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\curators\curators-02.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\curators\curators-01.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wemo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\Wemo_LOGO-2.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -815,7 +2255,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -892,6 +2332,19 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -914,12 +2367,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -928,6 +2378,30 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1145,7 +2619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1157,182 +2631,234 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="F4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
+      <c r="K4" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="A5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+      <c r="A6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+      <c r="A7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
@@ -1340,10 +2866,10 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
@@ -1768,8 +3294,9 @@
   <hyperlinks>
     <hyperlink ref="J2" r:id="rId1" xr:uid="{C765A748-DDEE-4DBA-A426-3F238EFEB8F9}"/>
     <hyperlink ref="J4" r:id="rId2" xr:uid="{080DD1D4-1DDE-4B01-80E7-E3EF2EB658FB}"/>
+    <hyperlink ref="J3" r:id="rId3" xr:uid="{778ACE66-D589-4F84-A173-0CB3D4084848}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80891007-485A-4350-A0DB-41AB6AC38734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79DA72B-1915-4838-B50E-23C1C399F7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="85">
   <si>
     <t>台灣</t>
   </si>
@@ -2248,6 +2248,300 @@
   </si>
   <si>
     <t>assets\images\logos\Wemo_LOGO-2.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>民偉視訊工程有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.meway.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>自</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1995</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年成立以來，民偉視訊工程有限公司專注於視訊、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、燈光、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>音響及整合工程服務，憑藉專業團隊、豐富經驗與完善設備，為各類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>活動打造高品質的視聽體驗。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>從企業活動、產品發表、展覽到大型演出，民偉以專業規劃、細緻執行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與熱忱服務，讓每一個精彩時刻，都能被看見、被聽見，完美呈現。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meway</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Since its establishment in 1995, Meway has specialized in video, LED displays, lighting, audio, and integrated technical production services. Backed by a professional team, extensive experience, and comprehensive equipment, Meway delivers high-quality audiovisual experiences for events of all scales.
+From corporate events and product launches to exhibitions and large-scale performances, Meway combines professional planning, meticulous execution, and dedicated service to ensure that every memorable moment is seen, heard, and presented at its best.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\民偉_LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\捷克中心台北_LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>捷克中心台北</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://taipei.czechcentres.gov.cz/zh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Czech Center Taipei</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奧地利台北辦事處</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.bmeia.gv.at/tw/%E5%A5%A7%E5%9C%B0%E5%88%A9-%E8%BE%A6%E4%BA%8B%E8%99%95-%E5%8F%B0%E5%8C%97</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\奧地利駐臺辦事處LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Austrian Office Taipei</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>達明機器人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.hongfoundation.org.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>洪建全基金會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HONG FOUNDATION</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>洪建全基金會</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LOGO.png</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\Panasonic LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣松下電器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panasonic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.panasonic.com/tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.wemoscooter.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://linktr.ee/c2x3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.philips.com.tw/c-m-so/monitors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.teamgroupinc.com/tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大藝術委員會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://canadacouncil.ca/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Techman Robot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tm-robot.com/zh-hant</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Canada Council for the Arts</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2367,7 +2661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2385,9 +2679,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2403,6 +2694,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2619,18 +2912,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
-  <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="10" width="21.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
+    <col min="6" max="10" width="21.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
@@ -2665,7 +2960,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -2681,16 +2976,16 @@
       <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J2" s="6" t="s">
@@ -2699,9 +2994,8 @@
       <c r="K2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -2717,31 +3011,30 @@
       <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -2753,14 +3046,14 @@
       <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
       <c r="J4" s="6" t="s">
         <v>27</v>
       </c>
@@ -2768,11 +3061,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2780,514 +3073,220 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="5"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="K5" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="5"/>
+      <c r="F7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="K7" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+    <row r="10" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+    <row r="11" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="12"/>
+      <c r="J11" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+    <row r="12" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="J12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+    <row r="14" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
+    <row r="15" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -3295,8 +3294,19 @@
     <hyperlink ref="J2" r:id="rId1" xr:uid="{C765A748-DDEE-4DBA-A426-3F238EFEB8F9}"/>
     <hyperlink ref="J4" r:id="rId2" xr:uid="{080DD1D4-1DDE-4B01-80E7-E3EF2EB658FB}"/>
     <hyperlink ref="J3" r:id="rId3" xr:uid="{778ACE66-D589-4F84-A173-0CB3D4084848}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{B5903743-4106-479D-BA5C-B7E2C65A7B31}"/>
+    <hyperlink ref="J13" r:id="rId5" xr:uid="{14798B1D-EC89-4886-8839-669D4A64B242}"/>
+    <hyperlink ref="J6" r:id="rId6" xr:uid="{640803BB-33DD-4E72-B45A-35A529B74554}"/>
+    <hyperlink ref="J12" r:id="rId7" xr:uid="{3731B83D-8452-4421-A73B-5A5CAD3B4AD0}"/>
+    <hyperlink ref="J11" r:id="rId8" xr:uid="{B46849EC-BF0A-4016-93F8-ADC8FB395686}"/>
+    <hyperlink ref="J9" r:id="rId9" xr:uid="{FEC8F1F0-3722-4C0E-8580-E9B401D3C972}"/>
+    <hyperlink ref="J8" r:id="rId10" xr:uid="{1B0FE1CE-CEE5-4AF0-BE91-EDF2C28FBAFC}"/>
+    <hyperlink ref="J7" r:id="rId11" xr:uid="{4F542517-B066-4E71-98B1-6D4BCEAF69BF}"/>
+    <hyperlink ref="J5" r:id="rId12" xr:uid="{CA637E00-D094-4176-B867-95E767F46936}"/>
+    <hyperlink ref="J14" r:id="rId13" xr:uid="{B29B9A08-56B8-41BB-AE20-EE127B70FA34}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{077337A1-5A55-4F74-95FE-7CDB7DC473C5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79DA72B-1915-4838-B50E-23C1C399F7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E795C5-29C6-4507-845F-35995851C6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="97">
   <si>
     <t>台灣</t>
   </si>
@@ -2544,12 +2544,182 @@
     <t>Canada Council for the Arts</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>合作單位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C-LAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>未來視覺實驗室</t>
+    </r>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>C-LAB’s Future Vision Lab</t>
+  </si>
+  <si>
+    <t>「未來視覺實驗室」為臺灣當代文化實驗場 C-LAB 推動的科技媒體實驗平台，聚焦沉浸式影像、空間運算與新型態視覺技術的研究與創作。平台透過實驗製作、跨域合作與展演，串聯藝術家、技術團隊與研究者，探索影像、聲音、空間與觀眾之間的新關係，並建立大型沉浸式內容的創作與測試環境，推動臺灣在未來影像與科技藝術領域的實驗發展。</t>
+  </si>
+  <si>
+    <t>Future Vision Lab is a technology and media experimentation platform initiated by Taiwan Contemporary Culture Lab (C-LAB). It focuses on immersive imaging, spatial computing, and emerging forms of visual technology, bringing together artists, technical teams, and researchers through experimental production, interdisciplinary collaboration, and public presentation. The platform investigates new relationships among image, sound, space, and audiences while providing an environment for developing and testing large-scale immersive content. Through these activities, Future Vision Lab supports experimentation in future-oriented visual culture and advances the development of technology-based artistic practices in Taiwan.</t>
+  </si>
+  <si>
+    <t>https://clab.org.tw/unit/future-vision-lab/</t>
+  </si>
+  <si>
+    <t>assets\images\logos\</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>噪流</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fluid Noise</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>噪流於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2011</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年所創立，致力於推廣實驗聲響、創意編程與音像藝術，以「推廣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>教育</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>培力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社群」四個面向，不定期辦講座、工作坊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、新銳培力以及創作者小聚，連結國內外團體，培養創作與執行人才。</t>
+    </r>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Founded in 2011, FluidNoise is dedicated to promoting experimental sound, creative coding, and audiovisual art. Focusing on four areas—outreach, education, artist development, and community—FluidNoise regularly organizes talks, workshops, emerging artist programs, and creator meetups, while connecting with local and international organizations and supporting the development of both creative and production talent.</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://fluidnoise.com/about/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2639,6 +2809,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2661,7 +2844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2696,6 +2879,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2912,7 +3101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
@@ -3062,47 +3251,53 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>36</v>
+      <c r="A5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>43</v>
+      <c r="F5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="6" t="s">
-        <v>79</v>
+      <c r="I5" s="14"/>
+      <c r="J5" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>65</v>
+    <row r="6" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
@@ -3110,181 +3305,225 @@
         <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
-      <c r="F7" s="11" t="s">
-        <v>35</v>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>39</v>
+      <c r="B8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>51</v>
+      <c r="J9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>57</v>
-      </c>
+      <c r="B10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>58</v>
+      <c r="J10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="13" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>73</v>
+      <c r="B12" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="12"/>
+        <v>56</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="13" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="F13" s="12"/>
       <c r="J13" s="13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>80</v>
+      <c r="B14" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="F14" s="12"/>
       <c r="J14" s="13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J17" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3294,19 +3533,21 @@
     <hyperlink ref="J2" r:id="rId1" xr:uid="{C765A748-DDEE-4DBA-A426-3F238EFEB8F9}"/>
     <hyperlink ref="J4" r:id="rId2" xr:uid="{080DD1D4-1DDE-4B01-80E7-E3EF2EB658FB}"/>
     <hyperlink ref="J3" r:id="rId3" xr:uid="{778ACE66-D589-4F84-A173-0CB3D4084848}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{B5903743-4106-479D-BA5C-B7E2C65A7B31}"/>
-    <hyperlink ref="J13" r:id="rId5" xr:uid="{14798B1D-EC89-4886-8839-669D4A64B242}"/>
-    <hyperlink ref="J6" r:id="rId6" xr:uid="{640803BB-33DD-4E72-B45A-35A529B74554}"/>
-    <hyperlink ref="J12" r:id="rId7" xr:uid="{3731B83D-8452-4421-A73B-5A5CAD3B4AD0}"/>
-    <hyperlink ref="J11" r:id="rId8" xr:uid="{B46849EC-BF0A-4016-93F8-ADC8FB395686}"/>
-    <hyperlink ref="J9" r:id="rId9" xr:uid="{FEC8F1F0-3722-4C0E-8580-E9B401D3C972}"/>
-    <hyperlink ref="J8" r:id="rId10" xr:uid="{1B0FE1CE-CEE5-4AF0-BE91-EDF2C28FBAFC}"/>
-    <hyperlink ref="J7" r:id="rId11" xr:uid="{4F542517-B066-4E71-98B1-6D4BCEAF69BF}"/>
-    <hyperlink ref="J5" r:id="rId12" xr:uid="{CA637E00-D094-4176-B867-95E767F46936}"/>
-    <hyperlink ref="J14" r:id="rId13" xr:uid="{B29B9A08-56B8-41BB-AE20-EE127B70FA34}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{077337A1-5A55-4F74-95FE-7CDB7DC473C5}"/>
+    <hyperlink ref="J12" r:id="rId4" xr:uid="{B5903743-4106-479D-BA5C-B7E2C65A7B31}"/>
+    <hyperlink ref="J15" r:id="rId5" xr:uid="{14798B1D-EC89-4886-8839-669D4A64B242}"/>
+    <hyperlink ref="J8" r:id="rId6" xr:uid="{640803BB-33DD-4E72-B45A-35A529B74554}"/>
+    <hyperlink ref="J14" r:id="rId7" xr:uid="{3731B83D-8452-4421-A73B-5A5CAD3B4AD0}"/>
+    <hyperlink ref="J13" r:id="rId8" xr:uid="{B46849EC-BF0A-4016-93F8-ADC8FB395686}"/>
+    <hyperlink ref="J11" r:id="rId9" xr:uid="{FEC8F1F0-3722-4C0E-8580-E9B401D3C972}"/>
+    <hyperlink ref="J10" r:id="rId10" xr:uid="{1B0FE1CE-CEE5-4AF0-BE91-EDF2C28FBAFC}"/>
+    <hyperlink ref="J9" r:id="rId11" xr:uid="{4F542517-B066-4E71-98B1-6D4BCEAF69BF}"/>
+    <hyperlink ref="J7" r:id="rId12" xr:uid="{CA637E00-D094-4176-B867-95E767F46936}"/>
+    <hyperlink ref="J16" r:id="rId13" xr:uid="{B29B9A08-56B8-41BB-AE20-EE127B70FA34}"/>
+    <hyperlink ref="J17" r:id="rId14" xr:uid="{077337A1-5A55-4F74-95FE-7CDB7DC473C5}"/>
+    <hyperlink ref="J5" r:id="rId15" xr:uid="{E0EBFE01-B149-431D-8F9F-3E94661A9305}"/>
+    <hyperlink ref="J6" r:id="rId16" xr:uid="{5C930DE0-6290-463C-9BF3-F5A27EC2AABC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E795C5-29C6-4507-845F-35995851C6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187AE8B8-C4DC-4DF0-9ED9-5977C327BD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="5265" windowWidth="28740" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="清冊一覽" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="142">
   <si>
     <t>台灣</t>
   </si>
@@ -171,10 +171,6 @@
   </si>
   <si>
     <t>執行單位</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>圖片來源</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1929,10 +1925,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>十銓科技</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>c2x3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2208,11 +2200,6 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEAMGROUP specializes in the development and production of its own-brand memory modules, memory cards, USB flash drives, solid-state drives (SSDs), peripheral products, mobile accessories, and industrial memory and storage solutions. In 2016, the company launched T-FORCE, its gaming product line, followed by T-CREATE, a product line designed for creators, in 2020.
-TEAMGROUP products have received numerous design awards and international recognition, including the COMPUTEX d&amp;i awards, Best Choice Award, Taiwan Good Design Product Award, Golden Pin Design Award, Taiwan Excellence Awards, Japan’s GOOD DESIGN AWARD, Germany’s iF Design Award 2021 and Red Dot Design Award. Its products have also earned widespread recognition from technology media around the world.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2227,14 +2214,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Philips</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TEAMGROUP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>assets\images\curators\curators-02.jpg</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2406,10 +2385,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Meway</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Since its establishment in 1995, Meway has specialized in video, LED displays, lighting, audio, and integrated technical production services. Backed by a professional team, extensive experience, and comprehensive equipment, Meway delivers high-quality audiovisual experiences for events of all scales.
 From corporate events and product launches to exhibitions and large-scale performances, Meway combines professional planning, meticulous execution, and dedicated service to ensure that every memorable moment is seen, heard, and presented at its best.</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2431,10 +2406,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Czech Center Taipei</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>奧地利台北辦事處</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2447,10 +2418,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Austrian Office Taipei</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>達明機器人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2459,10 +2426,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>洪建全基金會</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HONG FOUNDATION</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2497,14 +2460,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>台灣松下電器</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Panasonic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.panasonic.com/tw/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2525,14 +2480,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>加拿大藝術委員會</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://canadacouncil.ca/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Techman Robot</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2541,10 +2488,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Canada Council for the Arts</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>合作單位</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2568,17 +2511,7 @@
     <t>C-LAB’s Future Vision Lab</t>
   </si>
   <si>
-    <t>「未來視覺實驗室」為臺灣當代文化實驗場 C-LAB 推動的科技媒體實驗平台，聚焦沉浸式影像、空間運算與新型態視覺技術的研究與創作。平台透過實驗製作、跨域合作與展演，串聯藝術家、技術團隊與研究者，探索影像、聲音、空間與觀眾之間的新關係，並建立大型沉浸式內容的創作與測試環境，推動臺灣在未來影像與科技藝術領域的實驗發展。</t>
-  </si>
-  <si>
-    <t>Future Vision Lab is a technology and media experimentation platform initiated by Taiwan Contemporary Culture Lab (C-LAB). It focuses on immersive imaging, spatial computing, and emerging forms of visual technology, bringing together artists, technical teams, and researchers through experimental production, interdisciplinary collaboration, and public presentation. The platform investigates new relationships among image, sound, space, and audiences while providing an environment for developing and testing large-scale immersive content. Through these activities, Future Vision Lab supports experimentation in future-oriented visual culture and advances the development of technology-based artistic practices in Taiwan.</t>
-  </si>
-  <si>
     <t>https://clab.org.tw/unit/future-vision-lab/</t>
-  </si>
-  <si>
-    <t>assets\images\logos\</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>噪流</t>
@@ -2589,45 +2522,76 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>噪流於</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2011</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>年所創立，致力於推廣實驗聲響、創意編程與音像藝術，以「推廣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+    <t>https://fluidnoise.com/about/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team Group Inc. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Team Group Inc. specializes in the development and production of its own-brand memory modules, memory cards, USB flash drives, solid-state drives (SSDs), peripheral products, mobile accessories, and industrial memory and storage solutions. In 2016, the company launched T-FORCE, its gaming product line, followed by T-CREATE, a product line designed for creators, in 2020.
+Team Group Inc. products have received numerous design awards and international recognition, including the COMPUTEX d&amp;i awards, Best Choice Award, Taiwan Good Design Product Award, Golden Pin Design Award, Taiwan Excellence Awards, Japan’s GOOD DESIGN AWARD, Germany’s iF Design Award 2021 and Red Dot Design Award. Its products have also earned widespread recognition from technology media around the world.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>財團法人洪建全教育文化基金會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>財團法人洪建全教育文化基金會（Hong Foundation）由國際牌（National）創辦人洪建全先生於1971年創立，是台灣最早由企業贊助成立的文教領域非營利組織之一。
+基金會秉持「播種、開創」精神，長期致力於推動台灣文化藝術教育發展。其會務發展歷程屢創社會風氣之先，1970年代創辦《書評書目》雜誌並推動民歌運動；1990年代起開設著名的「敏隆講堂」，深耕文史哲藝的成人人文教育。近年來則轉向支持前衛原創的當代藝術，透過「銅鐘藝術賞」與「問問題計畫」等多面向贊助，積極為台灣創作者培育永續的生態系統。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Panasonic Taiwan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣松下電器股份有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>十銓科技股份有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MEWAY VISION</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Philips Monitors </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Austrian Office Taipei </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Czech Centre Taipei</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣互動體驗設計協會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>贊助單位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
       </rPr>
       <t>-</t>
     </r>
@@ -2635,54 +2599,491 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>教育</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>培力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>社群」四個面向，不定期辦講座、工作坊</t>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>多媒體贊助</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>關於圖片來源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Footer圖片來源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\TIEDA Logo.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\Wemo_LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\TIEDA Logo-2.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>十銓科技</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>LOGO.png</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\C-LAB未來視覺實驗室LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\C2x3LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TIEDA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣松下電器股份有限公司（Panasonic Taiwan）創立於1962年，是日本 Panasonic 集團在台的重要成員。公司從早期生產收音機與揚聲器起家，歷經數十年深耕，目前事業範疇已橫跨家庭電化、視聽影音、汽車電子、電子元件及智慧商用設備等多元領域，建立起從研發、生產、銷售到售後服務的一貫化完整體系。
+近年來松下電器更積極結合AI科技推動綠色轉型，打造智慧家電生態圈與淨零實証場域，致力於實現永續發展與提升大眾的生活品質。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>捷克中心臺北（Czech Centre Taipei）成立於2024年6月，隸屬於捷克外交部全球網路與捷克臺北經濟文化辦事處，是捷克推動公眾外交與文化深耕的重要據點，旨在加深臺灣民眾對當代捷克文化的認識，並促進雙邊互動。
+其活動範疇廣泛，定期舉辦展覽、電影放映、講座及研討會，特別聚焦於設計、文學、電影、創新和遊戲等領域，同時也提供藝術駐村計畫，攜手臺灣各大文化單位為雙邊建立深度交流平台 。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奧地利台北辦事處（Austrian Office Taipei）位於台北市松山區，是奧地利共和國設於台灣的官方代表機構，並致力於深化奧地利與台灣在文化、教育、學術及旅遊等領域的多元交流。
+在領務服務方面，辦事處主要負責為台灣公民與外籍居民辦理赴奧地利的短期簽證、打工度假簽證及居留許可，同時也代表希臘政府簽發申根簽證。此外，它也為在台的奧地利公民提供護照換發、文件公證及緊急急難救助等關鍵領事協助。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台灣互動體驗設計協會（Taiwan Interactive and Experiential Design Association，簡稱 TIEDA），主要宗旨為促進互動體驗設計、互動藝術與人機互動的研究及交流，致力於推廣互動體驗設計的發展。
+協會透過講座、工作坊、展覽與跨領域合作，串連設計、藝術、科技及產業領域的創作者與專業人才，建立知識分享與實務交流的平台，拓展互動體驗在臺灣的多元可能。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Founded in 1971 by Chien-Chuan Hong, founder of National, the Hong Foundation is one of Taiwan’s earliest nonprofit cultural and educational organizations established with corporate support.
+Guided by a spirit of “sowing seeds and pioneering new paths,” the Foundation has long been committed to advancing arts, culture, and education in Taiwan. Throughout its history, it has often been at the forefront of cultural development. In the 1970s, it founded Shu Ping Shu Mu (Book Review and Bibliography) magazine and played an active role in Taiwan’s folk music movement. Since the 1990s, its LEARNING PROGRAM has continued to foster adult learning in literature, history, philosophy, and the arts.
+In recent years, the Foundation has shifted its focus toward supporting experimental and original contemporary art. Through initiatives such as the TUNG CHUNG PRIZE and QUESTION PROJECT, it provides multifaceted support for artists and creators while actively fostering a sustainable creative ecosystem in Taiwan.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Established in June 2024, Czech Centre Taipei is part of the global network of Czech Centres under the Ministry of Foreign Affairs of the Czech Republic and works in close cooperation with the Czech Economic and Cultural Office in Taipei. As an important platform for Czech public diplomacy and cultural engagement, it aims to deepen the Taiwanese public’s understanding of contemporary Czech culture while fostering exchange between Taiwan and the Czech Republic.
+Its programs span a wide range of cultural activities, including exhibitions, film screenings, lectures, and seminars, with a particular focus on design, literature, film, innovation, and gaming. Czech Centre Taipei also supports artist residency programs and collaborates with cultural institutions across Taiwan to create platforms for meaningful and sustained exchange between the two sides.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Located in Taipei’s Songshan District, the Austrian Office Taipei is the official representation of the Republic of Austria in Taiwan. It is dedicated to strengthening exchanges between Austria and Taiwan across a wide range of fields, including culture, education, academia, and tourism.
+The Office also provides consular services, including applications for short-stay visas, working holiday visas, and residence permits for Austria. It also issues Schengen visas on behalf of Greece. For Austrian citizens in Taiwan, the Office provides essential consular assistance, including passport services, document authentication, and emergency support.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Taiwan Interactive and Experiential Design Association (TIEDA) is dedicated to advancing research, exchange, and development in interactive experience design, interactive art, and human-computer interaction.
+Through lectures, workshops, exhibitions, and interdisciplinary collaborations, TIEDA brings together creators and professionals from the fields of design, art, technology, and industry. By providing a platform for knowledge sharing and practical exchange, the Association seeks to expand the possibilities of interactive experiences in Taiwan.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Established in 1962, Panasonic Taiwan is a key member of the Panasonic Group in Taiwan. Beginning with the production of radios and speakers, the company has expanded over more than six decades into a diverse range of businesses, including home appliances, audiovisual products, automotive electronics, electronic components, and smart solutions for commercial applications. Today, it maintains an integrated operation encompassing research and development, manufacturing, sales, and after-sales service.
+In recent years, Panasonic Taiwan has increasingly integrated AI technologies into its green transformation initiatives, developing smart home appliance ecosystems and net-zero demonstration sites as part of its ongoing commitment to sustainability and improving quality of life.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">c2x3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>區塊鏈藝術媒體</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>c2x3 is a blockchain art media platform dedicated to the development of digital and generative art, with an ongoing focus on the evolving digital art markets and ecosystems in Taiwan and around the world.
+Through articles, interviews, talks, exhibitions, and community events, the team documents developments in digital art within a global context while sharing perspectives from artists and collectors. By connecting the art, technology, and Web3 communities, c2x3 actively promotes and supports the creation and development of digital and generative art in Taiwan.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">c2x3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>區塊鏈藝術媒體，長期關注數位藝術、生成藝術的發展，並持續探索全球與台灣數位藝術市場與生態圈。團隊透過文章、專訪、講座、展覽及社群活動，記錄數位藝術在全球脈動下所發生的事件，分享創作者與收藏者的觀點，並串連藝術、科技與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Web3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>社群，積極推廣支持數位藝術和生成藝術在台灣的創作與發展。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tieda-ixd.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中山社區大學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.zscc.tp.edu.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhongshan Community College</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>場地合作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北典藏植物園</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>財團法人臺北市會展產業發展基金會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.expopark.taipei/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.future.url.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Taipei Collectible Botanical Garden </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAIPEI EXPO FOUNDATION</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>財團法人臺北市會展產業發展基金會是由臺北市政府於民國100年成立，其宗旨在於有效活化與營運花博公園園區。該基金會主要負責管理園區內各項展覽場館，並致力於推展臺北市的會展、設計以及創新產業發展。
+同時，基金會積極爭取並協助舉辦各類國際性大型會議、展覽與賽會，以此提升臺北市的城市競爭力與國際能見度，為市民打造多元的休閒與產業交流空間。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北典藏植物園位於花博公園新生園區，是一座結合鑽石級綠建築與園藝智慧的展覽型植物溫室。園區以人類、植物與環境為主軸，將臺灣不同氣候與地域的植物移至室內，描繪出臺灣生態環境的縮影，是全台單位面積展示種類最多的植物溫室。
+場館內依植物生態劃分為臺灣原生植物區、熱帶/亞熱帶植物區、蘭花與蕨類展示區、多肉植物區、溫帶植物區及高山植物區等主題展區，總計展出近五百種植物，完整呈現豐富的生物多樣性，是一處不受天氣影響、適合全家大小親近自然的無圍牆環境教育落腳點。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超級浪台北空間</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hyper Wave Taipei Space</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.hyperwavemit.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\臺北典藏植物園LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assets\images\logos\財團法人臺北市會展產業發展基金會 LOGO.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>財團法人臺北市會展產業發展基金會</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LOGO-2.png</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「未來視覺實驗室」在台灣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> context </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>下主要指由臺灣當代文化實驗場（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C-LAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>）所推動的科技媒體實驗平台，特別是其專注於沉浸式影像的「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>FUTURE VISION LAB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>該平台打造了穹頂劇場（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>DOME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>），利用球形投影技術探索未來視覺與科技藝術的極限，具備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>＆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>的能量，整合影像運算、拼接、軟硬體系統、環繞音場及建築結構設計等技術，除策劃展演及陪伴創作者以外，亦進行各項跨域實驗，持續開創未來視覺及創新科技的新視野。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>噪流於2011年所創立，致力於推廣實驗聲響、創意編程與音像藝術，以「推廣-教育-培力-社群」四個面向，不定期辦講座、工作坊 、新銳培力以及創作者小聚，連結國內外團體，培養創作與執行人才。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術團體「超級浪」2022年立案於臺北市萬華區，團員組成基底為2020年文化部「MIT」計畫獲選藝術家，後陸續加入獨立藝術家與策展人。團名源自藝術之於當代社會的變異與不確定性，藉此以藝術浪人自居，將當代藝術創作的特質落實到生活的片段中，旨在現實環境中以藝術開啟對話的可能性。
+透過展覽、藝術家駐村、研究計畫、工作坊與公共活動，串聯不同文化背景的藝術工作者，探索藝術、地方與當代社會之間的關係。團隊的計畫遍及臺灣及海外，持續促進跨地域的對話與長期合作。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Established by the Taipei City Government in 2011, the TAIPEI EXPO FOUNDATION is dedicated to the effective operation and revitalization of Taipei Expo Park. The Foundation manages the exhibition venues throughout the park while promoting the development of Taipei’s convention and exhibition, design, and innovation industries.
+The Foundation also actively attracts and supports major international conferences, exhibitions, competitions, and events, helping to enhance Taipei’s global visibility and competitiveness while creating diverse spaces for recreation, cultural exchange, and industry engagement.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Located in the Xinsheng Area of Taipei Expo Park, the Taipei Collectible Botanical Garden is an exhibition greenhouse that combines Diamond-Level Green Building design with horticultural innovation. Centered on the relationship between people, plants, and the environment, the garden brings together plant species from Taiwan’s diverse climates and regions, creating a microcosm of the island’s ecological landscape. It features the greatest variety of plant species per unit area among botanical greenhouses in Taiwan.
+The greenhouse is organized into themed ecological zones, including native Taiwanese plants, tropical and subtropical plants, orchids and ferns, succulents, temperate plants, and alpine plants. With nearly 500 plant species on display, the garden showcases Taiwan’s rich biodiversity and offers a weather-independent, family-friendly destination for experiencing nature and environmental education.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C-LAB’s Future Vision Lab is a technology and media experimentation platform initiated by the Taiwan Contemporary Culture Lab (C-LAB), with a particular focus on immersive moving-image practices.
+At its core is DOME, a dome theater that uses spherical projection technology to explore the possibilities of future visual culture and technological art. With strong R&amp;D capabilities, the platform integrates image processing, projection stitching, hardware and software systems, surround sound, and architectural design. In addition to presenting exhibitions and performances and supporting creators in developing new works, the Future Vision Lab facilitates interdisciplinary experimentation, continually opening up new perspectives on future visual practices and innovative technologies.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Founded in 2011, Fluid Noise is dedicated to promoting experimental sound, creative coding, and audiovisual art. Its activities center on four key areas: promotion, education, creative development, and community building.
+Through lectures, workshops, emerging artist development programs, and informal gatherings for creators, Fluid Noise connects organizations and communities in Taiwan and abroad while cultivating creative and production talent in the fields of experimental sound and audiovisual art.</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hyper Wave was formally established as an art collective in Taipei’s Wanhua District in 2022. Its founding members were artists selected for the Ministry of Culture’s 2020 “MIT” program, with independent artists and curators later joining the collective.
+The name “Hyper Wave” reflects the shifting and uncertain nature of art in contemporary society. Embracing the identity of artistic wanderers, the collective seeks to bring the qualities of contemporary art into fragments of everyday life and to open up possibilities for dialogue through art within real-world contexts.
+Through exhibitions, artist residencies, research projects, workshops, and public programs, Hyper Wave connects art practitioners from diverse cultural backgrounds and explores the relationships between art, place, and contemporary society. Its projects extend across Taiwan and internationally, fostering cross-regional dialogue and long-term collaboration.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臺北市中山社區大學成立於</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2003 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年，由私立稻江護家承辦，校本部設於臺北市中山區新生北路。學校以「終身學習、公民實踐」為核心，整合地方文史與現代商業特色，開設人文涵養、生活藝能及社團活動等多元化課程。
+校方致力於提升現代公民素養，積極引導學員參與公共事務與地方創生。透過彈性的學習機制，為社區居民建構友善的知識共享平台，是學員充實自我、拓展人脈的教育機構管道。</t>
     </r>
     <r>
       <rPr>
@@ -2694,32 +3095,19 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、新銳培力以及創作者小聚，連結國內外團體，培養創作與執行人才。</t>
-    </r>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>Founded in 2011, FluidNoise is dedicated to promoting experimental sound, creative coding, and audiovisual art. Focusing on four areas—outreach, education, artist development, and community—FluidNoise regularly organizes talks, workshops, emerging artist programs, and creator meetups, while connecting with local and international organizations and supporting the development of both creative and production talent.</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://fluidnoise.com/about/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Established in 2003, Zhongshan Community College is operated by Daojiang High School of Nursing and Home Economics, with its main campus located on Xinsheng North Road in Taipei’s Zhongshan District. Guided by the principles of “lifelong learning and civic engagement,” the College integrates local history and culture with the district’s contemporary commercial character, offering a diverse range of courses in the humanities, practical and creative skills, and community activities.
+The College is committed to fostering civic literacy and encouraging learners to participate in public affairs and local revitalization. Through flexible learning opportunities, it provides community residents with an accessible and welcoming platform for knowledge sharing, personal growth, and social connection.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2822,6 +3210,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2844,30 +3239,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2877,13 +3251,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3101,430 +3491,591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
-    <col min="6" max="10" width="21.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="2" customWidth="1"/>
+    <col min="6" max="10" width="21.28515625" style="2" customWidth="1"/>
+    <col min="11" max="12" width="45.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="3" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="F3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="6" t="s">
+    <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="B11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>48</v>
       </c>
+      <c r="K18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>38</v>
+    <row r="19" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="15" t="s">
+    <row r="20" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>91</v>
+      <c r="B20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="21" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="J13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="J14" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>54</v>
+      <c r="L21" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3533,21 +4084,25 @@
     <hyperlink ref="J2" r:id="rId1" xr:uid="{C765A748-DDEE-4DBA-A426-3F238EFEB8F9}"/>
     <hyperlink ref="J4" r:id="rId2" xr:uid="{080DD1D4-1DDE-4B01-80E7-E3EF2EB658FB}"/>
     <hyperlink ref="J3" r:id="rId3" xr:uid="{778ACE66-D589-4F84-A173-0CB3D4084848}"/>
-    <hyperlink ref="J12" r:id="rId4" xr:uid="{B5903743-4106-479D-BA5C-B7E2C65A7B31}"/>
-    <hyperlink ref="J15" r:id="rId5" xr:uid="{14798B1D-EC89-4886-8839-669D4A64B242}"/>
-    <hyperlink ref="J8" r:id="rId6" xr:uid="{640803BB-33DD-4E72-B45A-35A529B74554}"/>
-    <hyperlink ref="J14" r:id="rId7" xr:uid="{3731B83D-8452-4421-A73B-5A5CAD3B4AD0}"/>
-    <hyperlink ref="J13" r:id="rId8" xr:uid="{B46849EC-BF0A-4016-93F8-ADC8FB395686}"/>
-    <hyperlink ref="J11" r:id="rId9" xr:uid="{FEC8F1F0-3722-4C0E-8580-E9B401D3C972}"/>
-    <hyperlink ref="J10" r:id="rId10" xr:uid="{1B0FE1CE-CEE5-4AF0-BE91-EDF2C28FBAFC}"/>
-    <hyperlink ref="J9" r:id="rId11" xr:uid="{4F542517-B066-4E71-98B1-6D4BCEAF69BF}"/>
-    <hyperlink ref="J7" r:id="rId12" xr:uid="{CA637E00-D094-4176-B867-95E767F46936}"/>
-    <hyperlink ref="J16" r:id="rId13" xr:uid="{B29B9A08-56B8-41BB-AE20-EE127B70FA34}"/>
-    <hyperlink ref="J17" r:id="rId14" xr:uid="{077337A1-5A55-4F74-95FE-7CDB7DC473C5}"/>
-    <hyperlink ref="J5" r:id="rId15" xr:uid="{E0EBFE01-B149-431D-8F9F-3E94661A9305}"/>
-    <hyperlink ref="J6" r:id="rId16" xr:uid="{5C930DE0-6290-463C-9BF3-F5A27EC2AABC}"/>
+    <hyperlink ref="J18" r:id="rId4" xr:uid="{B5903743-4106-479D-BA5C-B7E2C65A7B31}"/>
+    <hyperlink ref="J14" r:id="rId5" xr:uid="{14798B1D-EC89-4886-8839-669D4A64B242}"/>
+    <hyperlink ref="J13" r:id="rId6" xr:uid="{640803BB-33DD-4E72-B45A-35A529B74554}"/>
+    <hyperlink ref="J21" r:id="rId7" xr:uid="{3731B83D-8452-4421-A73B-5A5CAD3B4AD0}"/>
+    <hyperlink ref="J20" r:id="rId8" xr:uid="{B46849EC-BF0A-4016-93F8-ADC8FB395686}"/>
+    <hyperlink ref="J16" r:id="rId9" xr:uid="{FEC8F1F0-3722-4C0E-8580-E9B401D3C972}"/>
+    <hyperlink ref="J12" r:id="rId10" xr:uid="{1B0FE1CE-CEE5-4AF0-BE91-EDF2C28FBAFC}"/>
+    <hyperlink ref="J19" r:id="rId11" xr:uid="{4F542517-B066-4E71-98B1-6D4BCEAF69BF}"/>
+    <hyperlink ref="J11" r:id="rId12" xr:uid="{CA637E00-D094-4176-B867-95E767F46936}"/>
+    <hyperlink ref="J15" r:id="rId13" xr:uid="{077337A1-5A55-4F74-95FE-7CDB7DC473C5}"/>
+    <hyperlink ref="J7" r:id="rId14" xr:uid="{E0EBFE01-B149-431D-8F9F-3E94661A9305}"/>
+    <hyperlink ref="J9" r:id="rId15" xr:uid="{5C930DE0-6290-463C-9BF3-F5A27EC2AABC}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{4E0349AF-8D7F-4813-A13B-C02C8778EC6C}"/>
+    <hyperlink ref="J10" r:id="rId17" xr:uid="{AE715CF3-F1E5-435A-8991-BC1075E46ECA}"/>
+    <hyperlink ref="J6" r:id="rId18" xr:uid="{840EED14-B9D1-4FFC-82C9-1A8A01B9BE41}"/>
+    <hyperlink ref="J5" r:id="rId19" xr:uid="{03D1C1B0-F7CA-456C-A313-6DFB6618610F}"/>
+    <hyperlink ref="J8" r:id="rId20" xr:uid="{73857782-C19E-4C1B-B381-8F72BF54A6AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
 </worksheet>
 </file>
--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187AE8B8-C4DC-4DF0-9ED9-5977C327BD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AEBD59-0401-4EAD-BEC4-F735EBC3FBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="5265" windowWidth="28740" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="143">
   <si>
     <t>台灣</t>
   </si>
@@ -3100,6 +3100,32 @@
   <si>
     <t>Established in 2003, Zhongshan Community College is operated by Daojiang High School of Nursing and Home Economics, with its main campus located on Xinsheng North Road in Taipei’s Zhongshan District. Guided by the principles of “lifelong learning and civic engagement,” the College integrates local history and culture with the district’s contemporary commercial character, offering a diverse range of courses in the humanities, practical and creative skills, and community activities.
 The College is committed to fostering civic literacy and encouraging learners to participate in public affairs and local revitalization. Through flexible learning opportunities, it provides community residents with an accessible and welcoming platform for knowledge sharing, personal growth, and social connection.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>超級浪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LOGO.png</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3749,7 +3775,10 @@
         <v>128</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>49</v>
+        <v>142</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">

--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AEBD59-0401-4EAD-BEC4-F735EBC3FBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B668572D-7C19-45BB-BEA5-75AD5D77A6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="5265" windowWidth="28740" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="146">
   <si>
     <t>台灣</t>
   </si>
@@ -2238,9 +2238,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>assets\images\logos\</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2418,10 +2415,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>達明機器人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.hongfoundation.org.tw/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2477,10 +2470,6 @@
   </si>
   <si>
     <t>https://www.teamgroupinc.com/tw/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Techman Robot</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3125,6 +3114,228 @@
         <scheme val="minor"/>
       </rPr>
       <t>LOGO.png</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>達明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LOGO.png</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>達明機器人股份有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TECHMAN ROBOT INC. </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2015 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年創立於台灣的達明機器人，是全球唯一原生整合視覺與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>的機器人品牌，創立三年即躍升全球領先協作機器人廠商。如今更以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Physical AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>領航者之姿，推動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>機器人普及。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>在台北數位藝術節，藝術家王連晟運用搭載內建</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>視覺與原生軟體的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TM5S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">TM7S </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>協作機器人展出作品，讓精準動作與藝術創意交會，呈現人機共創的想像，展現智慧科技跨越產業、走入文化與生活的多元可能。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Founded in Taiwan in 2015, TECHMAN ROBOT INC. is the world’s only robotics brand with natively integrated vision and AI. Within just three years of its establishment, the company became one of the world’s leading collaborative robot manufacturers. Today, TECHMAN ROBOT continues to advance the adoption of AI-powered robotics as a pioneer in Physical AI.
+At the Taipei Digital Art Festival, artist Wang Lien-Cheng presents his work using TM5S and TM7S collaborative robots, equipped with built-in AI vision and native software. Bringing precise robotic movement together with artistic creativity, the work explores the possibilities of human-machine co-creation and demonstrates how intelligent technologies can move beyond industrial applications into culture and everyday life.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>中山社大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Logo.png</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3562,10 +3773,10 @@
         <v>6</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -3600,7 +3811,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>44</v>
@@ -3638,7 +3849,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>43</v>
@@ -3678,159 +3889,159 @@
     </row>
     <row r="5" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>121</v>
-      </c>
       <c r="K5" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="K6" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="L8" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -3838,22 +4049,22 @@
         <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>38</v>
@@ -3864,19 +4075,19 @@
         <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>37</v>
@@ -3890,25 +4101,25 @@
         <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="9" t="s">
+      <c r="K13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="L13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -3916,25 +4127,25 @@
         <v>32</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="K14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -3942,19 +4153,25 @@
         <v>32</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>142</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -3968,10 +4185,10 @@
         <v>45</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>46</v>
@@ -3982,25 +4199,25 @@
         <v>32</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4011,22 +4228,22 @@
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>48</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4037,7 +4254,7 @@
         <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>34</v>
@@ -4046,7 +4263,7 @@
         <v>41</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>39</v>
@@ -4057,54 +4274,54 @@
     </row>
     <row r="20" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="L20" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B668572D-7C19-45BB-BEA5-75AD5D77A6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210F38F9-0219-496F-90FF-84557F4ED22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="5265" windowWidth="28740" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="清冊一覽" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="145">
   <si>
     <t>台灣</t>
   </si>
@@ -1970,31 +1970,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>assets\images\logos\</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>十銓科技</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>LOGO-2.png</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>assets\images\logos\Philips logo.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2222,14 +2197,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>wemo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assets\images\logos\Wemo_LOGO-2.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>民偉視訊工程有限公司</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2610,10 +2577,6 @@
   </si>
   <si>
     <t>assets\images\logos\Wemo_LOGO.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assets\images\logos\TIEDA Logo-2.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2836,32 +2799,6 @@
   </si>
   <si>
     <r>
-      <t>assets\images\logos\</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>財團法人臺北市會展產業發展基金會</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> LOGO-2.png</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
@@ -3337,6 +3274,255 @@
       </rPr>
       <t>Logo.png</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WeMo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>重新定義拓展城市自由的多元可能，在「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> GO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>廣、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>多、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">GO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>」的服務升級，移動不再是從</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>點到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>點的通勤過程，而是一場雙倍有趣的感官探險。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>結合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> WeMo Fly </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>與</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> WeMo GO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>雙車款的隨心切換，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">WeMo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>讓「雙倍好租、雙倍好騎」成為一種無法抗拒的生活態度。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">WeMo Scooter </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>威摩科技股份有限公司</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeMo redefines urban mobility by opening up more possibilities for exploring the city with freedom and flexibility. With an upgraded experience built around going farther, discovering more, and enjoying every ride, getting around is no longer simply about traveling from Point A to Point B—it becomes a sensory adventure with twice the fun.
+With the freedom to switch between WeMo Fly and WeMo GO, WeMo makes “twice as easy to rent, twice as fun to ride” more than just a mobility experience—it becomes an irresistible way of life.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3773,10 +3959,10 @@
         <v>6</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -3811,10 +3997,10 @@
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -3849,10 +4035,10 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -3875,7 +4061,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>26</v>
@@ -3889,159 +4075,159 @@
     </row>
     <row r="5" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="L5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="J8" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="J9" s="10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4049,25 +4235,25 @@
         <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4075,19 +4261,19 @@
         <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>37</v>
@@ -4101,25 +4287,25 @@
         <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="J13" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4127,25 +4313,25 @@
         <v>32</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="J14" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4153,45 +4339,51 @@
         <v>32</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>45</v>
+      <c r="B16" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>142</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.2">
@@ -4199,25 +4391,25 @@
         <v>32</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="J17" s="12" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4225,25 +4417,25 @@
         <v>32</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="J18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="L18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4254,74 +4446,74 @@
         <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210F38F9-0219-496F-90FF-84557F4ED22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F546BE2-1801-47F1-A126-08F9AFF2784C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2835" yWindow="1845" windowWidth="28740" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="清冊一覽" sheetId="7" r:id="rId1"/>
+    <sheet name="單位與策展人" sheetId="7" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>

--- a/assets/2026臺北數位藝術節_關於清冊.xlsx
+++ b/assets/2026臺北數位藝術節_關於清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F546BE2-1801-47F1-A126-08F9AFF2784C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F82C209-D7C5-4540-93FD-0F95354CCEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1845" windowWidth="28740" windowHeight="19065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1335" yWindow="7500" windowWidth="28740" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="單位與策展人" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="151">
   <si>
     <t>台灣</t>
   </si>
@@ -3523,6 +3523,54 @@
   <si>
     <t>WeMo redefines urban mobility by opening up more possibilities for exploring the city with freedom and flexibility. With an upgraded experience built around going farther, discovering more, and enjoying every ride, getting around is no longer simply about traveling from Point A to Point B—it becomes a sensory adventure with twice the fun.
 With the freedom to switch between WeMo Fly and WeMo GO, WeMo makes “twice as easy to rent, twice as fun to ride” more than just a mobility experience—it becomes an irresistible way of life.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上銀科技股份有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">HIWIN TECHNOLOGIES CORP.  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.hiwin.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Founded in 1989 and headquartered in Taichung, Taiwan, HIWIN TECHNOLOGIES markets its products worldwide under the “HIWIN” brand. The company is a global leader in motion control and system technologies, as well as one of the world’s major manufacturers of ball screws and linear guideways.
+HIWIN TECHNOLOGIES specializes in the research, development, and manufacturing of high-speed, high-precision, energy-efficient key components. Its core products include ball screws, linear guideways, industrial robots, and medical robots. These technologies are widely applied across industries including semiconductors, AI robotics supply chains, automation equipment, and precision machinery. Building on its strong R&amp;D capabilities, HIWIN continues to advance smart manufacturing while expanding its global presence.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上銀科技成立於1989年，總部位於臺灣臺中，以自有品牌「HIWIN」行銷全球，是全球傳動控制與系統科技的領導品牌之一，也是全球重要的滾珠螺桿與線性滑軌製造商。
+上銀科技專注於高速、高精密及環保節能的關鍵零組件研發與製造，核心產品包含滾珠螺桿、線性滑軌、工業機器人以及醫療用機器人等。產品應用廣泛，涵蓋半導體、AI機器人供應鏈、自動化設備及精密機械等領域，除具備強大研發實力，更持續推動智慧製造與全球化佈局。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>assets\images\logos\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上銀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LOGO.png</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3914,7 +3962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62DD4C-B01B-4399-AF1E-5E7776919A9A}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="2" bestFit="1" customWidth="1"/>
@@ -4360,82 +4408,82 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>143</v>
+      <c r="B16" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>60</v>
+        <v>148</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>83</v>
+      <c r="B17" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>106</v>
+        <v>144</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>46</v>
+        <v>93</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>45</v>
+        <v>101</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4443,51 +4491,51 @@
         <v>32</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J20" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
@@ -4495,24 +4543,50 @@
         <v>84</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J22" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4522,25 +4596,26 @@
     <hyperlink ref="J2" r:id="rId1" xr:uid="{C765A748-DDEE-4DBA-A426-3F238EFEB8F9}"/>
     <hyperlink ref="J4" r:id="rId2" xr:uid="{080DD1D4-1DDE-4B01-80E7-E3EF2EB658FB}"/>
     <hyperlink ref="J3" r:id="rId3" xr:uid="{778ACE66-D589-4F84-A173-0CB3D4084848}"/>
-    <hyperlink ref="J18" r:id="rId4" xr:uid="{B5903743-4106-479D-BA5C-B7E2C65A7B31}"/>
+    <hyperlink ref="J19" r:id="rId4" xr:uid="{B5903743-4106-479D-BA5C-B7E2C65A7B31}"/>
     <hyperlink ref="J14" r:id="rId5" xr:uid="{14798B1D-EC89-4886-8839-669D4A64B242}"/>
     <hyperlink ref="J13" r:id="rId6" xr:uid="{640803BB-33DD-4E72-B45A-35A529B74554}"/>
-    <hyperlink ref="J21" r:id="rId7" xr:uid="{3731B83D-8452-4421-A73B-5A5CAD3B4AD0}"/>
-    <hyperlink ref="J20" r:id="rId8" xr:uid="{B46849EC-BF0A-4016-93F8-ADC8FB395686}"/>
-    <hyperlink ref="J16" r:id="rId9" xr:uid="{FEC8F1F0-3722-4C0E-8580-E9B401D3C972}"/>
+    <hyperlink ref="J22" r:id="rId7" xr:uid="{3731B83D-8452-4421-A73B-5A5CAD3B4AD0}"/>
+    <hyperlink ref="J21" r:id="rId8" xr:uid="{B46849EC-BF0A-4016-93F8-ADC8FB395686}"/>
+    <hyperlink ref="J17" r:id="rId9" xr:uid="{FEC8F1F0-3722-4C0E-8580-E9B401D3C972}"/>
     <hyperlink ref="J12" r:id="rId10" xr:uid="{1B0FE1CE-CEE5-4AF0-BE91-EDF2C28FBAFC}"/>
-    <hyperlink ref="J19" r:id="rId11" xr:uid="{4F542517-B066-4E71-98B1-6D4BCEAF69BF}"/>
+    <hyperlink ref="J20" r:id="rId11" xr:uid="{4F542517-B066-4E71-98B1-6D4BCEAF69BF}"/>
     <hyperlink ref="J11" r:id="rId12" xr:uid="{CA637E00-D094-4176-B867-95E767F46936}"/>
     <hyperlink ref="J15" r:id="rId13" xr:uid="{077337A1-5A55-4F74-95FE-7CDB7DC473C5}"/>
     <hyperlink ref="J7" r:id="rId14" xr:uid="{E0EBFE01-B149-431D-8F9F-3E94661A9305}"/>
     <hyperlink ref="J9" r:id="rId15" xr:uid="{5C930DE0-6290-463C-9BF3-F5A27EC2AABC}"/>
-    <hyperlink ref="J17" r:id="rId16" xr:uid="{4E0349AF-8D7F-4813-A13B-C02C8778EC6C}"/>
+    <hyperlink ref="J18" r:id="rId16" xr:uid="{4E0349AF-8D7F-4813-A13B-C02C8778EC6C}"/>
     <hyperlink ref="J10" r:id="rId17" xr:uid="{AE715CF3-F1E5-435A-8991-BC1075E46ECA}"/>
     <hyperlink ref="J6" r:id="rId18" xr:uid="{840EED14-B9D1-4FFC-82C9-1A8A01B9BE41}"/>
     <hyperlink ref="J5" r:id="rId19" xr:uid="{03D1C1B0-F7CA-456C-A313-6DFB6618610F}"/>
     <hyperlink ref="J8" r:id="rId20" xr:uid="{73857782-C19E-4C1B-B381-8F72BF54A6AE}"/>
+    <hyperlink ref="J16" r:id="rId21" xr:uid="{523C4666-C599-4974-BBE3-2470B065239B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>